--- a/artfynd/A 31066-2024 artfynd.xlsx
+++ b/artfynd/A 31066-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67833580</v>
+        <v>73557413</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>3518</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodtjärnarna, Hls</t>
+          <t>Bjåstabodarna, NO Gammelbodtjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599953.9166161818</v>
+        <v>600117</v>
       </c>
       <c r="R2" t="n">
-        <v>6872810.827429637</v>
+        <v>6872871</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-10-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst. Ett par bålar med apothecier.</t>
+          <t>2018-10-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,32 +757,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Med lövinslag, bläbär/gräs/mossa.</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>F-923077</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -820,6 +797,139 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>67833580</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gammelbodtjärnarna, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>599954</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6872811</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2017-10-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2017-10-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst. Ett par bålar med apothecier.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31066-2024 artfynd.xlsx
+++ b/artfynd/A 31066-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73557413</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -930,8 +940,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67833580</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>